--- a/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T00:32:33+00:00</t>
+    <t>2024-10-31T01:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T01:08:52+00:00</t>
+    <t>2024-10-31T03:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T03:13:53+00:00</t>
+    <t>2024-10-31T04:38:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
